--- a/mx-simulator-lab/올인원2.0_시뮬레이터_학습노트.xlsx
+++ b/mx-simulator-lab/올인원2.0_시뮬레이터_학습노트.xlsx
@@ -15,6 +15,8 @@
     <sheet name="M4 완납·연체" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="M5 원복·AS보상" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="M6 치트시트·시험" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="💡 쉬운예시" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="📋 18시트 설명" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +60,22 @@
     <font>
       <name val="Consolas"/>
       <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -159,6 +177,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1006,6 +1045,358 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>18개 시트 — 한 줄 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>한 줄 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>리스상각표(할인전·선납전)</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>순정 엔진, RATE로 내재이자율</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>리스상각표(선납후)</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>선납→채권↓→이자율 재계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>리스상각표(선납+단품+결합)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>전 할인 반영 엔진</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>리스상각표(결합·A해지·월할)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>해지 시 월할로 채권 끊기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>정상만기(CE)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>에어컨 전할인 72개월 청구</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>정상만기(MX)</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>갤탭, 파손보험 비과세</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>정상만기 첫달·막달 일할</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>일할 검증(1회차+막달=한달)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>⑧</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>중도해지(선납)</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>정산 5종 입문</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>중도해지(+단품)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>할인회수에 단품 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>⑩</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>중도해지(전할인)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>완전체, 계산기 기준 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>⑪</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>중도해지_MX</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>갤탭 버전(파손 비과세)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>⑫</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>중도완납</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>남은 값 일시 완납, 위약금 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>⑬</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>연체강제해지</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>연체이자(6%,365)·3회 초과 강제</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>⑭</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>연체강제해지_MX</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>갤탭 버전</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>⑮</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>연체강제해지(전할인)</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>할인까지 회수</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>⑯</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>할인원복(익익월)</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>결합 깨짐→21회차부터 정상가</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>⑰</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>AS보상</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>미사용 기간 보상 환급(ROUNDUP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>⑱</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>AS보상_MX</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>갤탭 버전</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2953,4 +3344,192 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>어려운 개념 — 비유로 쉽게</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>● 금융리스가 뭔데?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>구독 = 할부폰 판매. 폰 넘긴 첫 달 폰매출 잡고, 할부금엔 원금+이자. 구독도 동일 → 리스채권=제품값, 이자수익=할부이자.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>● IRR 왜 재계산?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>대출 숨은 이자율. 480만 빌려주고 매달 116,000×60 받으면 이자율 자동 결정. 면제로 덜 받으면 숨은 이자율 다시 풀어야(RATE). 정상15.11%→반값12.83%→면제10.69%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>● MIN(제품값,PV) 왜?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>받을 채권은 판 제품값을 못 넘음. PV가 더 커도 제품값으로 cap. → 제품매출은 고정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>● 에누리 왜 기간에 퍼져?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>구독료 깎으면 첫달 제품매출은 고정→깎인 건 '이자'. 이자는 매달 조금씩 인식→효과도 기간 분산. (포인트=매출차감=당월)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>● 100원 내리면 손익?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>이자수익에서 100원×기간 빠짐. 제품매출 그대로. 당월 아니라 기간에 얇게. 아주 크게 내리면 PV&lt;제품값 되어 제품매출도 타격(면제/반값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>● 할인 6단계 왜 빙 돌아?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>피자 똑같이 자르기. 59만÷72=8,191.67(소수점)→월 8,200 반올림 후 ×72=590,400. 깔끔 청구. 푼돈차=잡손익.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>● 경과 vs 잔여 왜 반대?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>헬스장 환불. 받은 할인=다닌 만큼(경과) 토해냄 / 미리 낸 선납=안 쓴 만큼(잔여) 환불.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>● 위약금 왜 비과세?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>벌금엔 부가세 없음. 위약금은 거래 아닌 손해배상→v+ 그대로(×1.1 안함). 연체이자·분실/파손료도 동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>● 연체이자 어떻게 쌓여?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>밀린 돈×6%×(연체일/365). 매달 또 밀리면 회차별 따로 누적. 3회 초과→강제해지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>● 익익월이 뭐야?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>다음다음 달부터 정상가. 결합 깨져도 이번·다음 청구는 이미 출발→두 박자 뒤(21회차)부터 원복. 회수는 경과만큼.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A9:B9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>